--- a/output/2020/sector_totals_v2.5_year2020.xlsx
+++ b/output/2020/sector_totals_v2.5_year2020.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1682.597123360775</v>
+        <v>1783.81015240719</v>
       </c>
       <c r="C3" t="n">
-        <v>108.1042452469288</v>
+        <v>99.64318336968235</v>
       </c>
       <c r="D3" t="n">
-        <v>668.0163298874863</v>
+        <v>702.8541145454159</v>
       </c>
       <c r="E3" t="n">
-        <v>2026.889834421561</v>
+        <v>1920.968226766637</v>
       </c>
       <c r="F3" t="n">
-        <v>175.2711442237958</v>
+        <v>172.6435431190611</v>
       </c>
       <c r="G3" t="n">
-        <v>80.60992038708542</v>
+        <v>74.67026501716694</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6273.1544609538</v>
+        <v>6374.367490000216</v>
       </c>
       <c r="C16" t="n">
-        <v>1006.897493019947</v>
+        <v>998.4364311427</v>
       </c>
       <c r="D16" t="n">
-        <v>5227.468988476169</v>
+        <v>5262.306773134098</v>
       </c>
       <c r="E16" t="n">
-        <v>8789.416191457443</v>
+        <v>8683.49458380252</v>
       </c>
       <c r="F16" t="n">
-        <v>4415.166079737307</v>
+        <v>4412.538478632573</v>
       </c>
       <c r="G16" t="n">
-        <v>116.2409565173855</v>
+        <v>110.301301147467</v>
       </c>
     </row>
   </sheetData>
